--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260612.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.61%</t>
+          <t>10.56%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.16%</t>
+          <t>10.06%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>375,900,486</t>
+          <t>375,416,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.34%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.89%</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>111,074,000</t>
+          <t>111,374,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>184,975,000</t>
+          <t>184,738,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>4.15%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,995,000</t>
+          <t>4,989,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
@@ -765,34 +765,34 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,306</t>
+          <t>2,186</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -809,78 +809,78 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>134,352,945</t>
+          <t>134,180,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -897,166 +897,166 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>28,522,000</t>
+          <t>28,485,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>25,874,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>97,767,000</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>25,907,000</t>
+          <t>226,605,516</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>226,896,516</t>
+          <t>97,767,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>62,491,000</t>
+          <t>62,411,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>329,875,000</t>
+          <t>334,875,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>49,897,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>49,497,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1210,68 +1210,68 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>85,399,080</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>85,399,080</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12,291,053,746</t>
+          <t>11,352,969,392</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,554,235,462</t>
+          <t>10,014,846,022</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-1,980,568,897</t>
+          <t>-2,133,639,432</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
